--- a/data/trans_bre/IQ2605_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 6,51</t>
+          <t>-12,0; 7,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 1,97</t>
+          <t>-11,51; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 3,95</t>
+          <t>-14,33; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 29,23</t>
+          <t>-9,58; 20,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 8,87</t>
+          <t>-14,9; 9,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,32</t>
+          <t>-12,51; 2,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 5,25</t>
+          <t>-16,71; 3,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 42,96</t>
+          <t>-9,55; 27,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,54%</t>
+          <t>-2,19%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 12,94</t>
+          <t>-0,66; 13,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,52</t>
+          <t>-7,22; 4,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,49</t>
+          <t>-5,42; 5,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 9,13</t>
+          <t>-13,9; 9,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 25,96</t>
+          <t>-0,98; 27,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 6,16</t>
+          <t>-9,08; 6,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 6,9</t>
+          <t>-6,33; 6,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 11,1</t>
+          <t>-15,17; 11,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 6,71</t>
+          <t>-13,58; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 18,75</t>
+          <t>2,75; 20,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 5,07</t>
+          <t>-10,45; 3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 20,57</t>
+          <t>-16,17; 16,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 14,95</t>
+          <t>-24,79; 13,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 32,01</t>
+          <t>4,13; 34,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 6,72</t>
+          <t>-12,93; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 35,25</t>
+          <t>-20,99; 27,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-14,43</t>
+          <t>-13,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-19,83%</t>
+          <t>-19,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 8,19</t>
+          <t>-7,88; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 4,95</t>
+          <t>-11,97; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 4,43</t>
+          <t>-13,03; 4,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 1,26</t>
+          <t>-28,84; 1,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 22,51</t>
+          <t>-17,53; 20,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 8,41</t>
+          <t>-17,61; 7,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 6,32</t>
+          <t>-16,94; 6,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 1,15</t>
+          <t>-37,07; 2,0</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,83%</t>
+          <t>-6,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,37</t>
+          <t>-3,1; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,45</t>
+          <t>-3,5; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,25</t>
+          <t>-6,86; 0,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,92</t>
+          <t>-13,23; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 10,57</t>
+          <t>-5,64; 10,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,28</t>
+          <t>-4,65; 5,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,31</t>
+          <t>-8,46; 0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 5,25</t>
+          <t>-16,57; 4,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2605_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-6,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.888279461916521</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.689367311076643</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.594242103088076</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.429150081978238</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.03675341356757627</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05200636886671983</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.0692864444738838</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.03779660135306397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-12,0; 7,12</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,51; 1,87</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,33; 2,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,58; 20,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,9; 9,11</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-12,51; 2,06</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,71; 3,63</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-9,55; 27,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-12.00375640860602</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.51302945154891</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.33310991945483</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.580982803986423</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1489966628721981</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.125093373368534</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1671153100080942</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.09552964727583593</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.118253368269027</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.873263151852788</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.882939629225292</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.95597673252962</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.09106620532661783</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.02061642230809278</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.03633102180243131</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2744737615496519</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 13,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,22; 4,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,42; 5,45</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,9; 9,5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 27,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-9,08; 6,47</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-6,33; 6,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-15,17; 11,37</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.399867075656951</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.307844296851679</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.04764614334245021</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.910341499936719</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1209480349435925</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01679556866981371</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.0005654411510371007</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.02193793248412568</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6556377252071435</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.224697237123516</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.417054053294027</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-13.89979624117125</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.009804112152680426</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.09080669121461028</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.06330427525203085</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1516675782791837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,58; 6,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,75; 20,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,45; 3,8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-16,17; 16,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-24,79; 13,02</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,13; 34,86</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-12,93; 5,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-20,99; 27,87</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.43173053390307</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.756021355516398</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.448239665597019</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.497071529291375</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.27946508893874</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06472370588657154</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.0666705271039479</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1136754406063595</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,55</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-13,97</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-5,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-5,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-19,22%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.245218420489254</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10.70486146290459</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.002533038046284</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8812815007836594</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.06438206634075253</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1683606036339365</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.03839135996577907</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01250098254751489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,88; 7,71</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 4,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-13,03; 4,27</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-28,84; 1,44</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-17,53; 20,16</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-17,61; 7,68</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-16,94; 6,42</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-37,07; 2,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.58254632839121</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.749981092697782</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.45449098769669</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-16.17132982533554</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2479449113208892</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.0412753807086671</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1292889805256519</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2099176009493293</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.152986026144626</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>20.26091302729232</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.803248588151562</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.82527580810406</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1301619381245747</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3486456692298352</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.05048992382227937</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2787268531606237</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1537119681903398</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.548529878224771</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.133409812264855</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-13.97046007277845</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.003734825619141346</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.05569048640066147</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.05770993532363498</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1922357516618418</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.881751967509063</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.97277926684169</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-13.03058737432531</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-28.83513466083575</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1752707547421608</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1760988133971328</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1693618806124116</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3706914745557617</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.70589461288616</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.619167320819793</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.273861121599761</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.443354067152622</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2015781599979951</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.07684719391808117</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06423296522301015</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.02000878575979942</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 5,48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 3,96</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 0,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 3,42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,64; 10,58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 5,57</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 0,17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-16,57; 4,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.106065584966409</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3736818697691713</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.159160033088659</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.107941800459526</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.02093118306917435</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.005102766104736466</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0399014313013596</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06690871548552733</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.100487736028702</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.4984941046588</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.859868753305517</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.23146662025233</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05644780080181084</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04651677879560448</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.08455027958582431</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1656696221126695</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.483694473083508</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.96071043787095</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.0948525551437846</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.424689944129816</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1058007112315439</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.05574048590538836</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.001694597755322028</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.04646814411696432</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
